--- a/Team-Data/2013-14/1-13-2013-14.xlsx
+++ b/Team-Data/2013-14/1-13-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -769,19 +836,19 @@
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
         <v>16</v>
@@ -793,10 +860,10 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>20</v>
@@ -811,11 +878,11 @@
         <v>22</v>
       </c>
       <c r="BB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC2" t="n">
         <v>14</v>
       </c>
-      <c r="BC2" t="n">
-        <v>13</v>
-      </c>
       <c r="BD2" t="n">
         <v>10</v>
       </c>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.333</v>
+        <v>0.342</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
@@ -861,43 +928,43 @@
         <v>36.5</v>
       </c>
       <c r="J3" t="n">
-        <v>82.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L3" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
         <v>18.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="O3" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.764</v>
+        <v>0.761</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T3" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U3" t="n">
         <v>19.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
         <v>6.8</v>
@@ -906,28 +973,28 @@
         <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
         <v>26</v>
@@ -939,10 +1006,10 @@
         <v>20</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -951,16 +1018,16 @@
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
@@ -984,16 +1051,16 @@
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-4.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
         <v>6</v>
@@ -1142,10 +1209,10 @@
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>25</v>
@@ -1160,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
@@ -1294,7 +1361,7 @@
         <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>16</v>
@@ -1303,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>0.472</v>
+        <v>0.486</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1413,43 +1480,43 @@
         <v>0.423</v>
       </c>
       <c r="L6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M6" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.332</v>
+        <v>0.329</v>
       </c>
       <c r="O6" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P6" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.765</v>
+        <v>0.769</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T6" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U6" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V6" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
         <v>6.8</v>
       </c>
       <c r="X6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
         <v>6.6</v>
@@ -1458,22 +1525,22 @@
         <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>91.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>15</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>15</v>
@@ -1494,19 +1561,19 @@
         <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN6" t="n">
         <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>7</v>
@@ -1515,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>24</v>
@@ -1664,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1709,7 +1776,7 @@
         <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY7" t="n">
         <v>28</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.59</v>
+        <v>0.579</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,28 +1838,28 @@
         <v>39.2</v>
       </c>
       <c r="J8" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L8" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.378</v>
+        <v>0.375</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.801</v>
+        <v>0.799</v>
       </c>
       <c r="R8" t="n">
         <v>9.699999999999999</v>
@@ -1807,40 +1874,40 @@
         <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>4.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
         <v>18.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>27</v>
@@ -1849,19 +1916,19 @@
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
       </c>
       <c r="AL8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN8" t="n">
         <v>7</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>20</v>
@@ -1873,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="AR8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
         <v>26</v>
@@ -1882,16 +1949,16 @@
         <v>28</v>
       </c>
       <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
         <v>7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1903,7 +1970,7 @@
         <v>29</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
         <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.514</v>
+        <v>0.528</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1962,73 +2029,73 @@
         <v>7.9</v>
       </c>
       <c r="M9" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.356</v>
+        <v>0.359</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.729</v>
+        <v>0.733</v>
       </c>
       <c r="R9" t="n">
         <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="T9" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="U9" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
       </c>
       <c r="X9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z9" t="n">
         <v>22.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB9" t="n">
         <v>102.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
         <v>7</v>
@@ -2040,10 +2107,10 @@
         <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2052,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2067,16 +2134,16 @@
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ9" t="n">
         <v>26</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
         <v>18</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>27</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2258,10 +2325,10 @@
         <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2419,7 +2486,7 @@
         <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.641</v>
+        <v>0.632</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2508,31 +2575,31 @@
         <v>8.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O12" t="n">
         <v>21.9</v>
       </c>
       <c r="P12" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="R12" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
         <v>34.3</v>
       </c>
       <c r="T12" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U12" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
@@ -2541,13 +2608,13 @@
         <v>7.4</v>
       </c>
       <c r="X12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA12" t="n">
         <v>24.6</v>
@@ -2556,22 +2623,22 @@
         <v>105.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
         <v>7</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
         <v>18</v>
@@ -2586,10 +2653,10 @@
         <v>6</v>
       </c>
       <c r="AM12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2616,10 +2683,10 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2762,16 +2829,16 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
@@ -2783,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2798,13 +2865,13 @@
         <v>25</v>
       </c>
       <c r="AW13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -2935,13 +3002,13 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>6</v>
@@ -2968,16 +3035,16 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
         <v>6</v>
@@ -2995,7 +3062,7 @@
         <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>-5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
         <v>23</v>
@@ -3123,10 +3190,10 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3138,7 +3205,7 @@
         <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
@@ -3153,10 +3220,10 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV15" t="n">
         <v>22</v>
@@ -3174,13 +3241,13 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -3287,25 +3354,25 @@
         <v>-0.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI16" t="n">
         <v>14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>10</v>
@@ -3323,10 +3390,10 @@
         <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR16" t="n">
         <v>6</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
         <v>14</v>
@@ -3356,7 +3423,7 @@
         <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>6.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3481,10 +3548,10 @@
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO17" t="n">
         <v>11</v>
@@ -3520,16 +3587,16 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -3573,19 +3640,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.189</v>
+        <v>0.194</v>
       </c>
       <c r="H18" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I18" t="n">
         <v>34.7</v>
@@ -3597,34 +3664,34 @@
         <v>0.42</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
         <v>20.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
         <v>15.2</v>
       </c>
       <c r="P18" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R18" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T18" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V18" t="n">
         <v>15.8</v>
@@ -3633,25 +3700,25 @@
         <v>7.1</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z18" t="n">
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,19 +3736,19 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="n">
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,25 +3757,25 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
         <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3717,7 +3784,7 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
@@ -3726,7 +3793,7 @@
         <v>29</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>14</v>
@@ -3854,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>11</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.405</v>
+        <v>0.417</v>
       </c>
       <c r="H20" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I20" t="n">
         <v>39</v>
       </c>
       <c r="J20" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.456</v>
@@ -3964,37 +4031,37 @@
         <v>6.2</v>
       </c>
       <c r="M20" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.386</v>
+        <v>0.381</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R20" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U20" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W20" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X20" t="n">
         <v>6.1</v>
@@ -4003,19 +4070,19 @@
         <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA20" t="n">
         <v>19.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.4</v>
+        <v>101.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>19</v>
@@ -4042,19 +4109,19 @@
         <v>26</v>
       </c>
       <c r="AM20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN20" t="n">
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
@@ -4063,7 +4130,7 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>11</v>
@@ -4081,16 +4148,16 @@
         <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA20" t="n">
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -4119,19 +4186,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.405</v>
+        <v>0.389</v>
       </c>
       <c r="H21" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
         <v>36.3</v>
@@ -4146,37 +4213,37 @@
         <v>8.6</v>
       </c>
       <c r="M21" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="N21" t="n">
         <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="P21" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>29.3</v>
+        <v>29</v>
       </c>
       <c r="T21" t="n">
-        <v>39.9</v>
+        <v>39.5</v>
       </c>
       <c r="U21" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="V21" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W21" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X21" t="n">
         <v>4.4</v>
@@ -4185,49 +4252,49 @@
         <v>3.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
         <v>19</v>
       </c>
-      <c r="AF21" t="n">
-        <v>18</v>
-      </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM21" t="n">
         <v>7</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4248,13 +4315,13 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
         <v>25</v>
@@ -4263,13 +4330,13 @@
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4409,7 +4476,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.263</v>
+        <v>0.27</v>
       </c>
       <c r="H23" t="n">
         <v>48.5</v>
@@ -4501,10 +4568,10 @@
         <v>36.1</v>
       </c>
       <c r="J23" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L23" t="n">
         <v>7.3</v>
@@ -4513,25 +4580,25 @@
         <v>21.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O23" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P23" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R23" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S23" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
         <v>20.2</v>
@@ -4543,25 +4610,25 @@
         <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>5.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,16 +4640,16 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>17</v>
@@ -4591,28 +4658,28 @@
         <v>15</v>
       </c>
       <c r="AN23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
         <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>15</v>
@@ -4630,14 +4697,14 @@
         <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB23" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC23" t="n">
         <v>25</v>
       </c>
-      <c r="BC23" t="n">
-        <v>27</v>
-      </c>
       <c r="BD23" t="n">
         <v>10</v>
       </c>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF24" t="n">
         <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH24" t="n">
         <v>3</v>
@@ -4791,7 +4858,7 @@
         <v>8</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>9</v>
@@ -4803,7 +4870,7 @@
         <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4812,13 +4879,13 @@
         <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>12</v>
       </c>
       <c r="BC24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
         <v>21</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="H25" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="I25" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J25" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.451</v>
+        <v>0.454</v>
       </c>
       <c r="L25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="O25" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="P25" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R25" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="S25" t="n">
         <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U25" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V25" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W25" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X25" t="n">
         <v>5.2</v>
@@ -4913,19 +4980,19 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>103</v>
+        <v>103.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4934,19 +5001,19 @@
         <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
@@ -4955,31 +5022,31 @@
         <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP25" t="n">
         <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
@@ -4994,13 +5061,13 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>6.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5134,16 +5201,16 @@
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -5289,25 +5356,25 @@
         <v>-1.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>16</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
@@ -5319,7 +5386,7 @@
         <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
@@ -5340,10 +5407,10 @@
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
@@ -5352,13 +5419,13 @@
         <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -5393,85 +5460,85 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.789</v>
+        <v>0.784</v>
       </c>
       <c r="H28" t="n">
         <v>48.1</v>
       </c>
       <c r="I28" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="J28" t="n">
-        <v>83.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K28" t="n">
         <v>0.491</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="N28" t="n">
         <v>0.398</v>
       </c>
       <c r="O28" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="P28" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
         <v>43.2</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
         <v>7.7</v>
       </c>
       <c r="X28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
         <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5498,7 +5565,7 @@
         <v>9</v>
       </c>
       <c r="AM28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5510,7 +5577,7 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
@@ -5519,13 +5586,13 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5540,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB28" t="n">
         <v>6</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
         <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.528</v>
+        <v>0.514</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J29" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.436</v>
+        <v>0.434</v>
       </c>
       <c r="L29" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M29" t="n">
         <v>22.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.358</v>
+        <v>0.353</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R29" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U29" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="V29" t="n">
         <v>14.6</v>
@@ -5638,58 +5705,58 @@
         <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
         <v>22.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF29" t="n">
         <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
       </c>
       <c r="AI29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK29" t="n">
         <v>26</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>24</v>
-      </c>
       <c r="AL29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AO29" t="n">
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
@@ -5713,22 +5780,22 @@
         <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB29" t="n">
         <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -5757,52 +5824,52 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.333</v>
+        <v>0.316</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J30" t="n">
         <v>81.7</v>
       </c>
       <c r="K30" t="n">
-        <v>0.439</v>
+        <v>0.436</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
       </c>
       <c r="M30" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="P30" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R30" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
         <v>41.2</v>
@@ -5811,7 +5878,7 @@
         <v>20.2</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W30" t="n">
         <v>7.1</v>
@@ -5829,34 +5896,34 @@
         <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.3</v>
+        <v>93.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.8</v>
+        <v>-7.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI30" t="n">
         <v>26</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>25</v>
       </c>
       <c r="AJ30" t="n">
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,31 +5932,31 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>25</v>
@@ -5898,13 +5965,13 @@
         <v>13</v>
       </c>
       <c r="AY30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>17</v>
       </c>
-      <c r="AZ30" t="n">
-        <v>18</v>
-      </c>
       <c r="BA30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
         <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>0.472</v>
+        <v>0.457</v>
       </c>
       <c r="H31" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I31" t="n">
         <v>37.3</v>
       </c>
       <c r="J31" t="n">
-        <v>83.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.443</v>
       </c>
       <c r="L31" t="n">
         <v>7.9</v>
@@ -5972,16 +6039,16 @@
         <v>0.38</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.729</v>
+        <v>0.733</v>
       </c>
       <c r="R31" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S31" t="n">
         <v>31.5</v>
@@ -5990,10 +6057,10 @@
         <v>42.7</v>
       </c>
       <c r="U31" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W31" t="n">
         <v>8.5</v>
@@ -6005,28 +6072,28 @@
         <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF31" t="n">
         <v>15</v>
       </c>
-      <c r="AF31" t="n">
-        <v>14</v>
-      </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
@@ -6035,16 +6102,16 @@
         <v>17</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM31" t="n">
         <v>17</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>16</v>
       </c>
       <c r="AN31" t="n">
         <v>5</v>
@@ -6053,13 +6120,13 @@
         <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS31" t="n">
         <v>19</v>
@@ -6071,10 +6138,10 @@
         <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>19</v>
@@ -6083,7 +6150,7 @@
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA31" t="n">
         <v>23</v>
@@ -6092,7 +6159,7 @@
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-13-2013-14</t>
+          <t>2014-01-13</t>
         </is>
       </c>
     </row>
